--- a/Тест2/259.xlsx
+++ b/Тест2/259.xlsx
@@ -234,7 +234,7 @@
     <t xml:space="preserve">Agar zichligi, pH qiymati va tuz miqdori</t>
   </si>
   <si>
-    <t xml:space="preserve">Koloniyalar soni, likopcha yuzasi, ekspozitsiya vaqti</t>
+    <t xml:space="preserve">Koloniyalar soni, likopcha yuzasi, ekspozitsiya</t>
   </si>
   <si>
     <t xml:space="preserve">Termostat quvvati, havo namligi va bosimi</t>
@@ -246,7 +246,7 @@
     <t xml:space="preserve">Likopcha rangi, xona hidi va havo harorati</t>
   </si>
   <si>
-    <t xml:space="preserve">To'g'ri javob: Koloniyalar soni, likopcha yuzasi, ekspozitsiya vaqti. Formulada koloniyalar soni, Petri likopchasining yuzasi va ekspozitsiya vaqti inobatga olinadi. Manba: Mavzu materiali (259.docx).</t>
+    <t xml:space="preserve">To'g'ri javob: Koloniyalar soni, likopcha yuzasi, ekspozitsiya. Formulada koloniyalar soni, Petri likopchasining yuzasi va ekspozitsiya vaqti inobatga olinadi. Manba: Mavzu materiali (259.docx).</t>
   </si>
   <si>
     <t xml:space="preserve">Sedimentatsion usulda hisoblangan qiymat qanday ifodalanadi?</t>
